--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/108.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/108.xlsx
@@ -426,13 +426,13 @@
         <v>-7.15227141444183</v>
       </c>
       <c r="E2">
-        <v>-19.57132859659564</v>
+        <v>-20.67717742079473</v>
       </c>
       <c r="F2">
-        <v>-1.721177794947307</v>
+        <v>-2.58462324378576</v>
       </c>
       <c r="G2">
-        <v>-14.48413608402809</v>
+        <v>-12.15574025017663</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.933237873300251</v>
       </c>
       <c r="E3">
-        <v>-20.33498781087913</v>
+        <v>-20.09541795045134</v>
       </c>
       <c r="F3">
-        <v>-1.736150535752908</v>
+        <v>-2.069856687235883</v>
       </c>
       <c r="G3">
-        <v>-15.07139435324049</v>
+        <v>-12.19540037516564</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.625119049738606</v>
       </c>
       <c r="E4">
-        <v>-20.63725892241711</v>
+        <v>-19.5039992450496</v>
       </c>
       <c r="F4">
-        <v>-1.889318153632745</v>
+        <v>-2.139406414374929</v>
       </c>
       <c r="G4">
-        <v>-14.32771533045702</v>
+        <v>-10.7336096079899</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.148193222074205</v>
       </c>
       <c r="E5">
-        <v>-21.46004642181876</v>
+        <v>-20.14769012592188</v>
       </c>
       <c r="F5">
-        <v>-1.681128716124159</v>
+        <v>-2.272979829708947</v>
       </c>
       <c r="G5">
-        <v>-14.69600620073222</v>
+        <v>-11.8664579138313</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.543452118438241</v>
       </c>
       <c r="E6">
-        <v>-21.04434609333664</v>
+        <v>-21.68444589432085</v>
       </c>
       <c r="F6">
-        <v>-1.862702708980796</v>
+        <v>-2.163598056006286</v>
       </c>
       <c r="G6">
-        <v>-15.72656570567949</v>
+        <v>-12.17784255860105</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.810649345237376</v>
       </c>
       <c r="E7">
-        <v>-22.63052109858132</v>
+        <v>-21.68523384879818</v>
       </c>
       <c r="F7">
-        <v>-1.897978734829013</v>
+        <v>-2.067723641173674</v>
       </c>
       <c r="G7">
-        <v>-15.15307216090897</v>
+        <v>-11.56006072583192</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.98704096297082</v>
       </c>
       <c r="E8">
-        <v>-22.09098511988545</v>
+        <v>-21.57953473698515</v>
       </c>
       <c r="F8">
-        <v>-1.490543742659868</v>
+        <v>-1.989139739139696</v>
       </c>
       <c r="G8">
-        <v>-14.73064933795683</v>
+        <v>-12.23047991485766</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.08842795151759</v>
       </c>
       <c r="E9">
-        <v>-22.42328001409429</v>
+        <v>-23.62103421827905</v>
       </c>
       <c r="F9">
-        <v>-1.701475904639123</v>
+        <v>-2.159938328820718</v>
       </c>
       <c r="G9">
-        <v>-14.36038481291363</v>
+        <v>-13.16814147501394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.13011950649924</v>
       </c>
       <c r="E10">
-        <v>-23.674139632967</v>
+        <v>-23.90826173916356</v>
       </c>
       <c r="F10">
-        <v>-1.569198055923084</v>
+        <v>-1.011258647074102</v>
       </c>
       <c r="G10">
-        <v>-14.13173945098685</v>
+        <v>-12.55049089110718</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.12855572575742</v>
       </c>
       <c r="E11">
-        <v>-23.65827186004413</v>
+        <v>-23.38993260424561</v>
       </c>
       <c r="F11">
-        <v>-1.09266231174721</v>
+        <v>-1.466559192879211</v>
       </c>
       <c r="G11">
-        <v>-14.09908801524881</v>
+        <v>-13.73282493989736</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.08374680322144</v>
       </c>
       <c r="E12">
-        <v>-25.03558005863302</v>
+        <v>-24.66729738148522</v>
       </c>
       <c r="F12">
-        <v>-1.313313708463511</v>
+        <v>-0.923119527048832</v>
       </c>
       <c r="G12">
-        <v>-12.97412284420397</v>
+        <v>-11.88170575041804</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.992035909619892</v>
       </c>
       <c r="E13">
-        <v>-25.93192356134125</v>
+        <v>-26.5886383334596</v>
       </c>
       <c r="F13">
-        <v>-0.7711215639417479</v>
+        <v>-1.406321972082437</v>
       </c>
       <c r="G13">
-        <v>-13.41624776200979</v>
+        <v>-11.58875500836926</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.857057922430604</v>
       </c>
       <c r="E14">
-        <v>-28.01116787348909</v>
+        <v>-26.7306875061322</v>
       </c>
       <c r="F14">
-        <v>-0.6492819728683854</v>
+        <v>-0.5884342452957477</v>
       </c>
       <c r="G14">
-        <v>-12.62685476046014</v>
+        <v>-11.54366446169937</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.66488732779281</v>
       </c>
       <c r="E15">
-        <v>-27.50192738590453</v>
+        <v>-28.42754294459835</v>
       </c>
       <c r="F15">
-        <v>-0.3168067753459703</v>
+        <v>-0.6455708869038437</v>
       </c>
       <c r="G15">
-        <v>-13.47974268040661</v>
+        <v>-11.45586553521175</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.409203530502165</v>
       </c>
       <c r="E16">
-        <v>-28.6377501795604</v>
+        <v>-27.04964604438846</v>
       </c>
       <c r="F16">
-        <v>-0.06144926955457788</v>
+        <v>-0.2136435557361255</v>
       </c>
       <c r="G16">
-        <v>-12.30247975953656</v>
+        <v>-11.1311722557969</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.086279066346165</v>
       </c>
       <c r="E17">
-        <v>-29.12264559087972</v>
+        <v>-27.534084079833</v>
       </c>
       <c r="F17">
-        <v>-0.392953620480912</v>
+        <v>0.4947240599916354</v>
       </c>
       <c r="G17">
-        <v>-12.52846076955707</v>
+        <v>-11.4155294785815</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.68512885326804</v>
       </c>
       <c r="E18">
-        <v>-30.40722875568755</v>
+        <v>-30.15099637514854</v>
       </c>
       <c r="F18">
-        <v>0.5695347485058615</v>
+        <v>0.5487601224110528</v>
       </c>
       <c r="G18">
-        <v>-11.48731604385903</v>
+        <v>-9.814568980183466</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.211602583727752</v>
       </c>
       <c r="E19">
-        <v>-30.50303768026783</v>
+        <v>-30.0519654413118</v>
       </c>
       <c r="F19">
-        <v>0.3709046708255821</v>
+        <v>0.1710279002040894</v>
       </c>
       <c r="G19">
-        <v>-11.02843720877068</v>
+        <v>-10.29601605715767</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.672007221943181</v>
       </c>
       <c r="E20">
-        <v>-32.29216756935127</v>
+        <v>-29.53801986923328</v>
       </c>
       <c r="F20">
-        <v>1.102885727737546</v>
+        <v>0.342822187503276</v>
       </c>
       <c r="G20">
-        <v>-10.78421588810121</v>
+        <v>-8.670699051123885</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.070792065047865</v>
       </c>
       <c r="E21">
-        <v>-32.14589106619251</v>
+        <v>-31.84198064706374</v>
       </c>
       <c r="F21">
-        <v>0.8922186433271866</v>
+        <v>1.32649688118405</v>
       </c>
       <c r="G21">
-        <v>-11.71058676487144</v>
+        <v>-9.23486900483325</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.43085122054435</v>
       </c>
       <c r="E22">
-        <v>-33.78104604630414</v>
+        <v>-32.23126412242211</v>
       </c>
       <c r="F22">
-        <v>0.92391032342349</v>
+        <v>0.3080622345470032</v>
       </c>
       <c r="G22">
-        <v>-10.05768452918741</v>
+        <v>-8.211249283484198</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.768147064622899</v>
       </c>
       <c r="E23">
-        <v>-33.13654004011048</v>
+        <v>-33.43708127457754</v>
       </c>
       <c r="F23">
-        <v>0.8058381472980597</v>
+        <v>1.091896605772007</v>
       </c>
       <c r="G23">
-        <v>-10.55357882468784</v>
+        <v>-9.661956084232134</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.098858059884668</v>
       </c>
       <c r="E24">
-        <v>-34.35827024992885</v>
+        <v>-33.23356033148781</v>
       </c>
       <c r="F24">
-        <v>1.298309195201588</v>
+        <v>1.32093687917646</v>
       </c>
       <c r="G24">
-        <v>-10.80836567877873</v>
+        <v>-7.500792628990109</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.451042373819194</v>
       </c>
       <c r="E25">
-        <v>-33.28312674373876</v>
+        <v>-35.3101215227861</v>
       </c>
       <c r="F25">
-        <v>1.14258772061892</v>
+        <v>1.293628919375771</v>
       </c>
       <c r="G25">
-        <v>-10.11153593742101</v>
+        <v>-7.766335327352851</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.83738741990815</v>
       </c>
       <c r="E26">
-        <v>-35.20458090756334</v>
+        <v>-34.95761152060702</v>
       </c>
       <c r="F26">
-        <v>0.6541491652322199</v>
+        <v>1.964904727908378</v>
       </c>
       <c r="G26">
-        <v>-9.515515166034117</v>
+        <v>-7.797421620407031</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.274018838162963</v>
       </c>
       <c r="E27">
-        <v>-34.53876163845257</v>
+        <v>-34.42635359239717</v>
       </c>
       <c r="F27">
-        <v>0.8751509613599056</v>
+        <v>1.138727528521875</v>
       </c>
       <c r="G27">
-        <v>-9.823461090609563</v>
+        <v>-7.710889245441354</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.775490448977256</v>
       </c>
       <c r="E28">
-        <v>-34.20912722272323</v>
+        <v>-35.53220468083327</v>
       </c>
       <c r="F28">
-        <v>0.7093250611978893</v>
+        <v>1.260099920380058</v>
       </c>
       <c r="G28">
-        <v>-10.1095704857069</v>
+        <v>-6.395391741493458</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.342692459101063</v>
       </c>
       <c r="E29">
-        <v>-34.33454783883967</v>
+        <v>-33.4339905910673</v>
       </c>
       <c r="F29">
-        <v>0.7243814671111731</v>
+        <v>0.9753618795461729</v>
       </c>
       <c r="G29">
-        <v>-9.165730385354191</v>
+        <v>-7.596774922046986</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.983017798086312</v>
       </c>
       <c r="E30">
-        <v>-33.02717286435123</v>
+        <v>-32.83021368009862</v>
       </c>
       <c r="F30">
-        <v>0.476224130784914</v>
+        <v>1.266226525691163</v>
       </c>
       <c r="G30">
-        <v>-8.846631588698191</v>
+        <v>-7.264577488925684</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.695611503343877</v>
       </c>
       <c r="E31">
-        <v>-33.86557454213132</v>
+        <v>-33.32647556117719</v>
       </c>
       <c r="F31">
-        <v>0.6359631872711595</v>
+        <v>0.9854663051255212</v>
       </c>
       <c r="G31">
-        <v>-8.860245376948328</v>
+        <v>-7.985967173655843</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.47304376874525</v>
       </c>
       <c r="E32">
-        <v>-32.96594110305652</v>
+        <v>-33.75168115660141</v>
       </c>
       <c r="F32">
-        <v>0.2099512277268326</v>
+        <v>0.369735844420232</v>
       </c>
       <c r="G32">
-        <v>-8.356485993369899</v>
+        <v>-6.706766542598523</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.317100511516326</v>
       </c>
       <c r="E33">
-        <v>-32.5791120606103</v>
+        <v>-31.15535983259874</v>
       </c>
       <c r="F33">
-        <v>0.4673382336550838</v>
+        <v>0.6187729069282641</v>
       </c>
       <c r="G33">
-        <v>-8.333809471172577</v>
+        <v>-7.477728922648772</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.219441962755523</v>
       </c>
       <c r="E34">
-        <v>-33.15718535311144</v>
+        <v>-32.22983312463569</v>
       </c>
       <c r="F34">
-        <v>-0.03957539991625413</v>
+        <v>0.2592440583978199</v>
       </c>
       <c r="G34">
-        <v>-8.643671629138739</v>
+        <v>-7.570416869259967</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.175877975084079</v>
       </c>
       <c r="E35">
-        <v>-31.17108043011637</v>
+        <v>-30.76793076734651</v>
       </c>
       <c r="F35">
-        <v>0.252686702037259</v>
+        <v>0.7907833981195815</v>
       </c>
       <c r="G35">
-        <v>-8.82702300865895</v>
+        <v>-7.515974841145661</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.185831549660577</v>
       </c>
       <c r="E36">
-        <v>-30.21498824135093</v>
+        <v>-30.51192707474489</v>
       </c>
       <c r="F36">
-        <v>0.007398830394297432</v>
+        <v>0.3159176426277509</v>
       </c>
       <c r="G36">
-        <v>-8.801065264902183</v>
+        <v>-7.607458579444538</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.241497151018497</v>
       </c>
       <c r="E37">
-        <v>-31.05225100791809</v>
+        <v>-32.24313778127023</v>
       </c>
       <c r="F37">
-        <v>-0.08727030986724127</v>
+        <v>0.4018284543394904</v>
       </c>
       <c r="G37">
-        <v>-8.217234231608625</v>
+        <v>-5.851552236566412</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.341872259498064</v>
       </c>
       <c r="E38">
-        <v>-29.70273631855128</v>
+        <v>-28.48417151206426</v>
       </c>
       <c r="F38">
-        <v>-0.1794029891414079</v>
+        <v>0.5824547948873254</v>
       </c>
       <c r="G38">
-        <v>-8.382207489174387</v>
+        <v>-5.93133513878431</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.482788412061704</v>
       </c>
       <c r="E39">
-        <v>-28.62866606070101</v>
+        <v>-30.29573093290769</v>
       </c>
       <c r="F39">
-        <v>0.08998374698379695</v>
+        <v>0.5886774908171554</v>
       </c>
       <c r="G39">
-        <v>-8.758675163575717</v>
+        <v>-9.028962508313416</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.658042636786487</v>
       </c>
       <c r="E40">
-        <v>-28.77552900124377</v>
+        <v>-30.12055370863198</v>
       </c>
       <c r="F40">
-        <v>-0.1124593058515686</v>
+        <v>0.6340057550983442</v>
       </c>
       <c r="G40">
-        <v>-8.831380470889894</v>
+        <v>-7.931347959577327</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.866690227907842</v>
       </c>
       <c r="E41">
-        <v>-28.93254478051172</v>
+        <v>-28.13142150076278</v>
       </c>
       <c r="F41">
-        <v>0.1895675910461451</v>
+        <v>0.2923944934904533</v>
       </c>
       <c r="G41">
-        <v>-9.230685447344959</v>
+        <v>-8.543597652797235</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.100692452902636</v>
       </c>
       <c r="E42">
-        <v>-28.05927385287257</v>
+        <v>-27.41410216099978</v>
       </c>
       <c r="F42">
-        <v>0.01467189619087709</v>
+        <v>0.1574724960246783</v>
       </c>
       <c r="G42">
-        <v>-9.433346815742501</v>
+        <v>-6.87957207602668</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.356804398822205</v>
       </c>
       <c r="E43">
-        <v>-26.04621318834684</v>
+        <v>-27.92683410204424</v>
       </c>
       <c r="F43">
-        <v>-0.0738267352872081</v>
+        <v>0.4363572927903822</v>
       </c>
       <c r="G43">
-        <v>-9.895470778953136</v>
+        <v>-7.224428461924319</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.633987785545246</v>
       </c>
       <c r="E44">
-        <v>-26.61640693607463</v>
+        <v>-26.03877743402624</v>
       </c>
       <c r="F44">
-        <v>0.1050343543252612</v>
+        <v>0.5157621069205345</v>
       </c>
       <c r="G44">
-        <v>-9.93060281819011</v>
+        <v>-9.581694123666557</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.924266063415354</v>
       </c>
       <c r="E45">
-        <v>-25.78136538600824</v>
+        <v>-26.28401241543762</v>
       </c>
       <c r="F45">
-        <v>-0.2090983037969646</v>
+        <v>0.1579852554470112</v>
       </c>
       <c r="G45">
-        <v>-9.889787703212178</v>
+        <v>-7.624858897374273</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.229189824871146</v>
       </c>
       <c r="E46">
-        <v>-24.44733581351065</v>
+        <v>-23.24930990088543</v>
       </c>
       <c r="F46">
-        <v>0.2187691987296333</v>
+        <v>1.09074351834731</v>
       </c>
       <c r="G46">
-        <v>-9.648138860245313</v>
+        <v>-7.66542135829213</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.54726644951828</v>
       </c>
       <c r="E47">
-        <v>-23.87574276731448</v>
+        <v>-23.91553899689389</v>
       </c>
       <c r="F47">
-        <v>0.036615348691036</v>
+        <v>0.8317229719007386</v>
       </c>
       <c r="G47">
-        <v>-8.794853912490154</v>
+        <v>-8.239238103386262</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.874625009884876</v>
       </c>
       <c r="E48">
-        <v>-23.23687018278635</v>
+        <v>-24.63668036871936</v>
       </c>
       <c r="F48">
-        <v>0.6775861641596262</v>
+        <v>0.8866984029549306</v>
       </c>
       <c r="G48">
-        <v>-9.459740961966675</v>
+        <v>-7.785012040469211</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.216398192588831</v>
       </c>
       <c r="E49">
-        <v>-23.57292371042156</v>
+        <v>-23.02325753537054</v>
       </c>
       <c r="F49">
-        <v>0.3926103818811375</v>
+        <v>0.39041852173333</v>
       </c>
       <c r="G49">
-        <v>-9.697898585194292</v>
+        <v>-7.868601159696065</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.570119164809788</v>
       </c>
       <c r="E50">
-        <v>-22.75268574188624</v>
+        <v>-22.90211632719135</v>
       </c>
       <c r="F50">
-        <v>0.1099772226177658</v>
+        <v>0.7221200241015304</v>
       </c>
       <c r="G50">
-        <v>-10.20331170443868</v>
+        <v>-11.06705390530379</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.935386201958742</v>
       </c>
       <c r="E51">
-        <v>-21.54740974237474</v>
+        <v>-20.92021156383838</v>
       </c>
       <c r="F51">
-        <v>0.5154324166942202</v>
+        <v>0.4812282982652258</v>
       </c>
       <c r="G51">
-        <v>-10.32270551332219</v>
+        <v>-7.580250690273623</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.316658260197141</v>
       </c>
       <c r="E52">
-        <v>-21.65667276323181</v>
+        <v>-20.3196226985711</v>
       </c>
       <c r="F52">
-        <v>0.962772351758426</v>
+        <v>0.3608640295362493</v>
       </c>
       <c r="G52">
-        <v>-10.75466520673685</v>
+        <v>-7.943347386820215</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.704755726771771</v>
       </c>
       <c r="E53">
-        <v>-20.18481455583676</v>
+        <v>-21.29250646895698</v>
       </c>
       <c r="F53">
-        <v>0.3662542162262656</v>
+        <v>1.060310956703262</v>
       </c>
       <c r="G53">
-        <v>-9.868830541112004</v>
+        <v>-9.608613265340241</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.098780623219735</v>
       </c>
       <c r="E54">
-        <v>-20.33131521845891</v>
+        <v>-20.27225486045087</v>
       </c>
       <c r="F54">
-        <v>0.3216673407705823</v>
+        <v>0.2895747308513238</v>
       </c>
       <c r="G54">
-        <v>-10.49010031239883</v>
+        <v>-8.730794623985116</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.495271536527845</v>
       </c>
       <c r="E55">
-        <v>-18.85778147568103</v>
+        <v>-19.63608124643131</v>
       </c>
       <c r="F55">
-        <v>-0.046835211834389</v>
+        <v>0.5014288657498945</v>
       </c>
       <c r="G55">
-        <v>-10.9304566517841</v>
+        <v>-8.525354060926722</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.879417244651481</v>
       </c>
       <c r="E56">
-        <v>-18.67597682969508</v>
+        <v>-19.65381927911936</v>
       </c>
       <c r="F56">
-        <v>0.3318893945211281</v>
+        <v>0.5886302738751957</v>
       </c>
       <c r="G56">
-        <v>-11.34315229342326</v>
+        <v>-8.667388298570405</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.247521434189799</v>
       </c>
       <c r="E57">
-        <v>-17.71752530597165</v>
+        <v>-19.6797040365472</v>
       </c>
       <c r="F57">
-        <v>0.2118100841787146</v>
+        <v>0.1594564359543831</v>
       </c>
       <c r="G57">
-        <v>-11.52312073351569</v>
+        <v>-8.386414015213594</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.590009722203186</v>
       </c>
       <c r="E58">
-        <v>-17.30301596615356</v>
+        <v>-17.36874223790088</v>
       </c>
       <c r="F58">
-        <v>0.06840974634528663</v>
+        <v>0.3907680927773114</v>
       </c>
       <c r="G58">
-        <v>-10.67290700914017</v>
+        <v>-10.14329159967332</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.893562862565663</v>
       </c>
       <c r="E59">
-        <v>-17.44760561274446</v>
+        <v>-17.43800977632221</v>
       </c>
       <c r="F59">
-        <v>0.2022001939388376</v>
+        <v>1.024187511001981</v>
       </c>
       <c r="G59">
-        <v>-10.46833925101659</v>
+        <v>-9.177890592453492</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.156326800767365</v>
       </c>
       <c r="E60">
-        <v>-15.99848487334193</v>
+        <v>-16.44650492081679</v>
       </c>
       <c r="F60">
-        <v>-0.07841754743352296</v>
+        <v>0.2840047884349</v>
       </c>
       <c r="G60">
-        <v>-10.87243152972688</v>
+        <v>-8.817195750088413</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.367944900277436</v>
       </c>
       <c r="E61">
-        <v>-16.26331909025851</v>
+        <v>-17.07644282612778</v>
       </c>
       <c r="F61">
-        <v>-0.6723478631993377</v>
+        <v>0.03937878234677514</v>
       </c>
       <c r="G61">
-        <v>-11.19773183513023</v>
+        <v>-8.058898885257621</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.520460368544956</v>
       </c>
       <c r="E62">
-        <v>-15.39234409894125</v>
+        <v>-16.28623316873732</v>
       </c>
       <c r="F62">
-        <v>-0.2997656011355788</v>
+        <v>0.03417829179199985</v>
       </c>
       <c r="G62">
-        <v>-11.08693810795402</v>
+        <v>-10.18023159198955</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.615266847228387</v>
       </c>
       <c r="E63">
-        <v>-14.3387131085246</v>
+        <v>-13.91067721684559</v>
       </c>
       <c r="F63">
-        <v>-0.009288630935098609</v>
+        <v>0.336099986029558</v>
       </c>
       <c r="G63">
-        <v>-10.74246234375728</v>
+        <v>-10.99962808347876</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.642180011207909</v>
       </c>
       <c r="E64">
-        <v>-15.15203609725021</v>
+        <v>-14.56019624376575</v>
       </c>
       <c r="F64">
-        <v>-0.8481092019905312</v>
+        <v>0.2619586183767939</v>
       </c>
       <c r="G64">
-        <v>-11.15870170468064</v>
+        <v>-10.73056791560429</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.601123576451107</v>
       </c>
       <c r="E65">
-        <v>-14.25136337339065</v>
+        <v>-14.16959724670815</v>
       </c>
       <c r="F65">
-        <v>-0.916236622298971</v>
+        <v>-0.4500430451470483</v>
       </c>
       <c r="G65">
-        <v>-11.51225004648925</v>
+        <v>-10.57334490336194</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.495826763730699</v>
       </c>
       <c r="E66">
-        <v>-14.6788920759808</v>
+        <v>-13.77787971657066</v>
       </c>
       <c r="F66">
-        <v>-0.5217109077350531</v>
+        <v>0.01920389425159319</v>
       </c>
       <c r="G66">
-        <v>-11.42899561186146</v>
+        <v>-8.764407457640067</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.321427168804354</v>
       </c>
       <c r="E67">
-        <v>-14.45859992940366</v>
+        <v>-14.52676704864113</v>
       </c>
       <c r="F67">
-        <v>-0.8396913324432826</v>
+        <v>-0.1610273150451065</v>
       </c>
       <c r="G67">
-        <v>-11.36567131698573</v>
+        <v>-10.43237378150351</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.084590755197629</v>
       </c>
       <c r="E68">
-        <v>-13.67902312898321</v>
+        <v>-14.46126267212017</v>
       </c>
       <c r="F68">
-        <v>-1.036528823063904</v>
+        <v>-1.143233313320717</v>
       </c>
       <c r="G68">
-        <v>-11.43224730242687</v>
+        <v>-9.880344347564096</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.791659027679285</v>
       </c>
       <c r="E69">
-        <v>-13.48871400881087</v>
+        <v>-13.26890640895255</v>
       </c>
       <c r="F69">
-        <v>-1.467886237458496</v>
+        <v>-0.7383132445864707</v>
       </c>
       <c r="G69">
-        <v>-10.68503440402388</v>
+        <v>-9.365028501653303</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.444553018902234</v>
       </c>
       <c r="E70">
-        <v>-14.8619148814748</v>
+        <v>-14.98859441336537</v>
       </c>
       <c r="F70">
-        <v>-1.493953302889791</v>
+        <v>-0.8307913530676048</v>
       </c>
       <c r="G70">
-        <v>-10.47047532625179</v>
+        <v>-8.368560888708656</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.058566373126541</v>
       </c>
       <c r="E71">
-        <v>-14.01214673393546</v>
+        <v>-14.49161250491958</v>
       </c>
       <c r="F71">
-        <v>-2.030848037870651</v>
+        <v>-1.004734425409653</v>
       </c>
       <c r="G71">
-        <v>-9.273334765174621</v>
+        <v>-9.63018729709359</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.643028602135926</v>
       </c>
       <c r="E72">
-        <v>-14.22139846088189</v>
+        <v>-15.02911519878601</v>
       </c>
       <c r="F72">
-        <v>-1.677242844637626</v>
+        <v>-1.449755760113423</v>
       </c>
       <c r="G72">
-        <v>-9.418371320545196</v>
+        <v>-9.920056972098054</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.204524626190621</v>
       </c>
       <c r="E73">
-        <v>-14.83509725840138</v>
+        <v>-13.57218737019425</v>
       </c>
       <c r="F73">
-        <v>-2.172876599285043</v>
+        <v>-1.830321827205364</v>
       </c>
       <c r="G73">
-        <v>-9.795147429773113</v>
+        <v>-9.429192789248244</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.761041144253612</v>
       </c>
       <c r="E74">
-        <v>-13.64284062166193</v>
+        <v>-14.87752000290523</v>
       </c>
       <c r="F74">
-        <v>-1.584367119803149</v>
+        <v>-1.765482197118635</v>
       </c>
       <c r="G74">
-        <v>-8.523408296541971</v>
+        <v>-9.793113072406259</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.316458280378203</v>
       </c>
       <c r="E75">
-        <v>-13.95389244430079</v>
+        <v>-14.31862026935257</v>
       </c>
       <c r="F75">
-        <v>-2.177281857133131</v>
+        <v>-1.550973144694092</v>
       </c>
       <c r="G75">
-        <v>-8.549270884873515</v>
+        <v>-9.054680722896343</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.87686199400789</v>
       </c>
       <c r="E76">
-        <v>-14.72179936720347</v>
+        <v>-14.62069665650823</v>
       </c>
       <c r="F76">
-        <v>-2.169473665994343</v>
+        <v>-2.518520353409762</v>
       </c>
       <c r="G76">
-        <v>-8.5062212580136</v>
+        <v>-7.975775699492208</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.452265016882678</v>
       </c>
       <c r="E77">
-        <v>-15.77027242572538</v>
+        <v>-14.21090598660612</v>
       </c>
       <c r="F77">
-        <v>-2.168831681257173</v>
+        <v>-2.229926262315845</v>
       </c>
       <c r="G77">
-        <v>-8.334321341735851</v>
+        <v>-7.388017043991995</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.041110587376254</v>
       </c>
       <c r="E78">
-        <v>-15.05046242525817</v>
+        <v>-14.37518996665638</v>
       </c>
       <c r="F78">
-        <v>-2.253837915765056</v>
+        <v>-2.385598863221748</v>
       </c>
       <c r="G78">
-        <v>-7.752826538192617</v>
+        <v>-6.501772225672215</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.64851106499626</v>
       </c>
       <c r="E79">
-        <v>-15.59251170702829</v>
+        <v>-16.37974162852171</v>
       </c>
       <c r="F79">
-        <v>-2.748618451987589</v>
+        <v>-2.447394243103188</v>
       </c>
       <c r="G79">
-        <v>-6.938378128815048</v>
+        <v>-6.905759505292608</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.277603054135233</v>
       </c>
       <c r="E80">
-        <v>-16.31056465958054</v>
+        <v>-16.98367703608066</v>
       </c>
       <c r="F80">
-        <v>-2.010787464477056</v>
+        <v>-2.262771029836846</v>
       </c>
       <c r="G80">
-        <v>-6.57117334287603</v>
+        <v>-8.085043658643276</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.924224247815209</v>
       </c>
       <c r="E81">
-        <v>-15.65274041133031</v>
+        <v>-15.94824145422683</v>
       </c>
       <c r="F81">
-        <v>-2.678950268309943</v>
+        <v>-2.02672276820471</v>
       </c>
       <c r="G81">
-        <v>-6.136811795279857</v>
+        <v>-5.413778218548417</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.593517989997618</v>
       </c>
       <c r="E82">
-        <v>-16.70589591197615</v>
+        <v>-17.00092146510186</v>
       </c>
       <c r="F82">
-        <v>-3.162574352351572</v>
+        <v>-2.968183030671418</v>
       </c>
       <c r="G82">
-        <v>-7.013938098885941</v>
+        <v>-5.260436891410887</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.284304807148348</v>
       </c>
       <c r="E83">
-        <v>-16.98773907726554</v>
+        <v>-17.40637838537863</v>
       </c>
       <c r="F83">
-        <v>-2.846181907954509</v>
+        <v>-2.31523485092575</v>
       </c>
       <c r="G83">
-        <v>-6.720652672238093</v>
+        <v>-5.848543356396402</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.992733282975121</v>
       </c>
       <c r="E84">
-        <v>-18.15607178582247</v>
+        <v>-18.2928860425422</v>
       </c>
       <c r="F84">
-        <v>-2.849743059419144</v>
+        <v>-2.091713161158748</v>
       </c>
       <c r="G84">
-        <v>-5.042678622618339</v>
+        <v>-4.895847239054747</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.724092920010957</v>
       </c>
       <c r="E85">
-        <v>-18.96761961273707</v>
+        <v>-18.42509031272213</v>
       </c>
       <c r="F85">
-        <v>-2.484268189671405</v>
+        <v>-2.704706695965188</v>
       </c>
       <c r="G85">
-        <v>-5.615776780190952</v>
+        <v>-3.9168718182435</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.475736466062454</v>
       </c>
       <c r="E86">
-        <v>-19.06836910245972</v>
+        <v>-19.79450990958966</v>
       </c>
       <c r="F86">
-        <v>-3.263196969137031</v>
+        <v>-2.866573828309225</v>
       </c>
       <c r="G86">
-        <v>-5.024451436855623</v>
+        <v>-4.867828888158648</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.248051183001785</v>
       </c>
       <c r="E87">
-        <v>-21.24405179707491</v>
+        <v>-22.57278758345753</v>
       </c>
       <c r="F87">
-        <v>-3.403039468975435</v>
+        <v>-3.123118384588829</v>
       </c>
       <c r="G87">
-        <v>-5.579184597360025</v>
+        <v>-5.5737738630085</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.0437935575421</v>
       </c>
       <c r="E88">
-        <v>-21.57258352938338</v>
+        <v>-22.84672856160353</v>
       </c>
       <c r="F88">
-        <v>-3.22762687286082</v>
+        <v>-3.673157653517312</v>
       </c>
       <c r="G88">
-        <v>-5.66903100610074</v>
+        <v>-5.40271393944997</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8614884023993729</v>
       </c>
       <c r="E89">
-        <v>-22.43926099886736</v>
+        <v>-22.51153997250378</v>
       </c>
       <c r="F89">
-        <v>-3.360256777723049</v>
+        <v>-3.194628029002899</v>
       </c>
       <c r="G89">
-        <v>-5.253848198519522</v>
+        <v>-4.284978940111364</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.7046195325194572</v>
       </c>
       <c r="E90">
-        <v>-24.50740149274839</v>
+        <v>-26.18110284361331</v>
       </c>
       <c r="F90">
-        <v>-3.991474395391078</v>
+        <v>-3.192996145219384</v>
       </c>
       <c r="G90">
-        <v>-5.286611195790577</v>
+        <v>-4.423899298495135</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5754615450245442</v>
       </c>
       <c r="E91">
-        <v>-25.48875803800262</v>
+        <v>-25.81665578395001</v>
       </c>
       <c r="F91">
-        <v>-4.00024846292153</v>
+        <v>-3.499619652835232</v>
       </c>
       <c r="G91">
-        <v>-4.915705191932506</v>
+        <v>-3.611646026340833</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4741259011056167</v>
       </c>
       <c r="E92">
-        <v>-27.03743274998977</v>
+        <v>-29.25560158774492</v>
       </c>
       <c r="F92">
-        <v>-4.248882938871802</v>
+        <v>-4.211969230668251</v>
       </c>
       <c r="G92">
-        <v>-5.130083802518826</v>
+        <v>-2.519527523716814</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.4042304725233665</v>
       </c>
       <c r="E93">
-        <v>-28.40880864762861</v>
+        <v>-29.16975530598151</v>
       </c>
       <c r="F93">
-        <v>-4.1676880227842</v>
+        <v>-4.033276299638549</v>
       </c>
       <c r="G93">
-        <v>-5.168083629398756</v>
+        <v>-3.687704742088762</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.3650290871234447</v>
       </c>
       <c r="E94">
-        <v>-29.97061367000101</v>
+        <v>-30.76772472177916</v>
       </c>
       <c r="F94">
-        <v>-4.444181322858022</v>
+        <v>-5.055369016726359</v>
       </c>
       <c r="G94">
-        <v>-5.933861679385083</v>
+        <v>-4.861522380321396</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.3551361171106391</v>
       </c>
       <c r="E95">
-        <v>-32.44393484724434</v>
+        <v>-33.64785456879054</v>
       </c>
       <c r="F95">
-        <v>-4.765889400878849</v>
+        <v>-4.690570094779304</v>
       </c>
       <c r="G95">
-        <v>-5.456739252426226</v>
+        <v>-5.668551947753062</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.3752917520535157</v>
       </c>
       <c r="E96">
-        <v>-33.78676777321284</v>
+        <v>-34.07637047871437</v>
       </c>
       <c r="F96">
-        <v>-4.806881161806382</v>
+        <v>-4.865435140040669</v>
       </c>
       <c r="G96">
-        <v>-5.592503075669812</v>
+        <v>-5.628570263051228</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.4190532779657554</v>
       </c>
       <c r="E97">
-        <v>-35.18604812768695</v>
+        <v>-36.70832636468339</v>
       </c>
       <c r="F97">
-        <v>-4.910600215943505</v>
+        <v>-4.960213624799376</v>
       </c>
       <c r="G97">
-        <v>-6.281835225764195</v>
+        <v>-5.704140076786799</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4858860791734406</v>
       </c>
       <c r="E98">
-        <v>-38.17680859470571</v>
+        <v>-36.31986933583142</v>
       </c>
       <c r="F98">
-        <v>-4.944438195980463</v>
+        <v>-5.163858638736205</v>
       </c>
       <c r="G98">
-        <v>-6.929407269071525</v>
+        <v>-6.518568798835013</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5652865206798056</v>
       </c>
       <c r="E99">
-        <v>-40.18905866238408</v>
+        <v>-40.16878015577772</v>
       </c>
       <c r="F99">
-        <v>-4.931939788607024</v>
+        <v>-5.499449326060549</v>
       </c>
       <c r="G99">
-        <v>-6.878308805726293</v>
+        <v>-6.646375659796943</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6603576991064849</v>
       </c>
       <c r="E100">
-        <v>-41.78179995493987</v>
+        <v>-42.17342691559721</v>
       </c>
       <c r="F100">
-        <v>-5.346072131227803</v>
+        <v>-5.32291429211514</v>
       </c>
       <c r="G100">
-        <v>-7.068704967934632</v>
+        <v>-7.04909638789539</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.753677664437376</v>
       </c>
       <c r="E101">
-        <v>-44.15663587946438</v>
+        <v>-44.13306064378045</v>
       </c>
       <c r="F101">
-        <v>-5.448529581810463</v>
+        <v>-5.547581614000213</v>
       </c>
       <c r="G101">
-        <v>-7.178520891086128</v>
+        <v>-6.076161695975081</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8655710432673176</v>
       </c>
       <c r="E102">
-        <v>-44.82048526238182</v>
+        <v>-45.94347888917395</v>
       </c>
       <c r="F102">
-        <v>-5.24536833443687</v>
+        <v>-5.266701280161166</v>
       </c>
       <c r="G102">
-        <v>-7.740476020242868</v>
+        <v>-6.927064476878082</v>
       </c>
     </row>
   </sheetData>
